--- a/artfynd/A 944-2025 artfynd.xlsx
+++ b/artfynd/A 944-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107785890</v>
+        <v>107785892</v>
       </c>
       <c r="B2" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4660</v>
+        <v>2014</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549766.0728807477</v>
+        <v>549742</v>
       </c>
       <c r="R2" t="n">
-        <v>6584077.737666389</v>
+        <v>6584144</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,12 +763,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Lövrik barrskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Asphögstubbe</t>
+          <t>Liggande aspstam</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,42 +786,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107785892</v>
+        <v>107785898</v>
       </c>
       <c r="B3" t="n">
-        <v>90174</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2014</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549742.2365320588</v>
+        <v>549861</v>
       </c>
       <c r="R3" t="n">
-        <v>6584144.153197004</v>
+        <v>6584079</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,19 +858,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,12 +875,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Lövrik barrskog</t>
+          <t>Ek-aspbestånd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Liggande aspstam</t>
+          <t>Basen av ekstam</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,6 +895,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>107785890</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Silverlingska hagarna, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>549766</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6584077</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-11-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Asphögstubbe</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 944-2025 artfynd.xlsx
+++ b/artfynd/A 944-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107785892</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107785898</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,8 +1021,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107785890</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>